--- a/AtchisonRegime/Outputs/Brazil/df_regZScores_Brazil.xlsx
+++ b/AtchisonRegime/Outputs/Brazil/df_regZScores_Brazil.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E341"/>
+  <dimension ref="A1:E342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6062,7 +6062,7 @@
         <v>-1.106168929183249</v>
       </c>
       <c r="C331" t="n">
-        <v>0.07010286730686353</v>
+        <v>0.08584304244701514</v>
       </c>
       <c r="D331" t="n">
         <v>0.6607631425232638</v>
@@ -6079,7 +6079,7 @@
         <v>-1.023152096709701</v>
       </c>
       <c r="C332" t="n">
-        <v>0.06777076014117203</v>
+        <v>0.07461153673370037</v>
       </c>
       <c r="D332" t="n">
         <v>0.6738196246178002</v>
@@ -6096,7 +6096,7 @@
         <v>-0.8887081705708955</v>
       </c>
       <c r="C333" t="n">
-        <v>0.08108255332278663</v>
+        <v>0.07532937712790448</v>
       </c>
       <c r="D333" t="n">
         <v>0.64392862120351</v>
@@ -6113,7 +6113,7 @@
         <v>-0.8060211384898766</v>
       </c>
       <c r="C334" t="n">
-        <v>0.03461839485758089</v>
+        <v>0.03958576536912412</v>
       </c>
       <c r="D334" t="n">
         <v>0.5453937035152667</v>
@@ -6130,7 +6130,7 @@
         <v>-0.7401941763003826</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.0362272390278989</v>
+        <v>-0.03478208068685314</v>
       </c>
       <c r="D335" t="n">
         <v>0.4012988812070913</v>
@@ -6147,7 +6147,7 @@
         <v>-0.6714028499367534</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.1204405614412703</v>
+        <v>-0.1167003150752939</v>
       </c>
       <c r="D336" t="n">
         <v>0.2692656463854147</v>
@@ -6164,7 +6164,7 @@
         <v>-0.5590277466514001</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.1675986740596273</v>
+        <v>-0.1715903141306255</v>
       </c>
       <c r="D337" t="n">
         <v>0.2201519689621168</v>
@@ -6181,7 +6181,7 @@
         <v>-0.4698383242787347</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.1760527105930659</v>
+        <v>-0.1828161926752659</v>
       </c>
       <c r="D338" t="n">
         <v>0.1470370271165108</v>
@@ -6198,7 +6198,7 @@
         <v>-0.449811882553294</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.1470744605152078</v>
+        <v>-0.1566516972167822</v>
       </c>
       <c r="D339" t="n">
         <v>0.1763511896644202</v>
@@ -6215,7 +6215,7 @@
         <v>-0.3853200776072436</v>
       </c>
       <c r="C340" t="n">
-        <v>-0.08209173015700538</v>
+        <v>-0.09485529935348186</v>
       </c>
       <c r="D340" t="n">
         <v>0.1371594861448566</v>
@@ -6229,16 +6229,33 @@
         <v>45747</v>
       </c>
       <c r="B341" t="n">
-        <v>-0.3084661278453371</v>
+        <v>-0.253891578687139</v>
       </c>
       <c r="C341" t="n">
-        <v>-0.02718857488385517</v>
+        <v>-0.04580605020778437</v>
       </c>
       <c r="D341" t="n">
         <v>0.1110546272241258</v>
       </c>
       <c r="E341" t="n">
         <v>-0.1283410707788303</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B342" t="n">
+        <v>-0.05005178341911259</v>
+      </c>
+      <c r="C342" t="n">
+        <v>-0.02169872933148871</v>
+      </c>
+      <c r="D342" t="n">
+        <v>-0.1433469846859853</v>
+      </c>
+      <c r="E342" t="n">
+        <v>-0.2934007498358872</v>
       </c>
     </row>
   </sheetData>
